--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -413,927 +413,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Distance 1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Distance 2</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Angle</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Area</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Measured by operator 7 on tool HRM-2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fiducial 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>127.23011</v>
-      </c>
-      <c r="D2" t="n">
-        <v>89.41513999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>94.56939</v>
-      </c>
-      <c r="F2" t="n">
-        <v>534.62199</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>126.55004</v>
+        <v>17.35467</v>
       </c>
       <c r="D3" t="n">
-        <v>88.84989</v>
+        <v>17.08455</v>
       </c>
       <c r="E3" t="n">
-        <v>95.81447</v>
+        <v>17.35366</v>
       </c>
       <c r="F3" t="n">
-        <v>541.52728</v>
+        <v>44.48804</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05269</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.86567</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>126.14672</v>
+        <v>18.02035</v>
       </c>
       <c r="D4" t="n">
-        <v>89.03778</v>
+        <v>17.44972</v>
       </c>
       <c r="E4" t="n">
-        <v>95.90978</v>
+        <v>17.65866</v>
       </c>
       <c r="F4" t="n">
-        <v>536.51629</v>
+        <v>45.12237</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05306</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.88522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>127.04576</v>
+        <v>17.57313</v>
       </c>
       <c r="D5" t="n">
-        <v>89.78941</v>
+        <v>17.07968</v>
       </c>
       <c r="E5" t="n">
-        <v>93.72769</v>
+        <v>17.38165</v>
       </c>
       <c r="F5" t="n">
-        <v>534.08942</v>
+        <v>44.46734</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05341</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.93508</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>126.75084</v>
+        <v>17.74972</v>
       </c>
       <c r="D6" t="n">
-        <v>90.30083</v>
+        <v>17.27131</v>
       </c>
       <c r="E6" t="n">
-        <v>97.04568</v>
+        <v>17.2765</v>
       </c>
       <c r="F6" t="n">
-        <v>543.65479</v>
+        <v>43.95704</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05325</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.92173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>128.74484</v>
+        <v>17.65497</v>
       </c>
       <c r="D7" t="n">
-        <v>91.27396</v>
+        <v>17.37532</v>
       </c>
       <c r="E7" t="n">
-        <v>97.27330000000001</v>
+        <v>17.51167</v>
       </c>
       <c r="F7" t="n">
-        <v>545.73184</v>
+        <v>44.79846</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05337</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.87987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>128.05395</v>
+        <v>17.83341</v>
       </c>
       <c r="D8" t="n">
-        <v>89.78473</v>
+        <v>17.4204</v>
       </c>
       <c r="E8" t="n">
-        <v>93.72801</v>
+        <v>17.48057</v>
       </c>
       <c r="F8" t="n">
-        <v>536.91137</v>
+        <v>44.60333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.90762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>126.97997</v>
+        <v>17.39634</v>
       </c>
       <c r="D9" t="n">
-        <v>90.07781</v>
+        <v>17.15163</v>
       </c>
       <c r="E9" t="n">
-        <v>94.38045</v>
+        <v>17.16345</v>
       </c>
       <c r="F9" t="n">
-        <v>532.77996</v>
+        <v>45.44577</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.87069</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.77385</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17.32404</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.41982</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45.33481</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.88886</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>127.23253</v>
-      </c>
-      <c r="D10" t="n">
-        <v>89.72725</v>
-      </c>
-      <c r="E10" t="n">
-        <v>94.43731</v>
-      </c>
-      <c r="F10" t="n">
-        <v>539.99215</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
+      <c r="C11" t="n">
+        <v>17.5801</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.33032</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.53088</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.85869</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05258</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.86528</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Micro Bump 3</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>9.06565</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25.78988</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.956810000000001</v>
+        <v>0.65827</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23735</v>
+        <v>1.18676</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.015890000000001</v>
+        <v>0.64297</v>
       </c>
       <c r="D14" t="n">
-        <v>25.50915</v>
+        <v>1.16884</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.092599999999999</v>
+        <v>0.62493</v>
       </c>
       <c r="D15" t="n">
-        <v>25.57135</v>
+        <v>1.1703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.11016</v>
+        <v>0.62464</v>
       </c>
       <c r="D16" t="n">
-        <v>25.10487</v>
+        <v>1.18738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.04609</v>
+        <v>0.63806</v>
       </c>
       <c r="D17" t="n">
-        <v>25.4869</v>
+        <v>1.15846</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.920260000000001</v>
+        <v>0.63994</v>
       </c>
       <c r="D18" t="n">
-        <v>24.62765</v>
+        <v>1.17115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.940189999999999</v>
+        <v>0.63637</v>
       </c>
       <c r="D19" t="n">
-        <v>25.09069</v>
+        <v>1.17144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.14951</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>9.099909999999999</v>
-      </c>
-      <c r="D20" t="n">
-        <v>25.88093</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C21" t="n">
+        <v>0.62327</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.14452</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>18.33749</v>
-      </c>
-      <c r="D22" t="n">
-        <v>17.53358</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.56324</v>
-      </c>
-      <c r="F22" t="n">
-        <v>44.76148</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05274</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.9461</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.79618</v>
+        <v>0.77425</v>
       </c>
       <c r="D23" t="n">
-        <v>17.3196</v>
+        <v>0.08523</v>
       </c>
       <c r="E23" t="n">
-        <v>17.41705</v>
+        <v>0.62864</v>
       </c>
       <c r="F23" t="n">
-        <v>45.64145</v>
+        <v>1.0287</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05271</v>
+        <v>0.1165</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9323</v>
+        <v>0.00795</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09636</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.13333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.7055</v>
+        <v>0.77862</v>
       </c>
       <c r="D24" t="n">
-        <v>17.19137</v>
+        <v>0.08543000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>17.53365</v>
+        <v>0.62735</v>
       </c>
       <c r="F24" t="n">
-        <v>44.12838</v>
+        <v>0.99818</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05317</v>
+        <v>0.11225</v>
       </c>
       <c r="H24" t="n">
-        <v>1.93098</v>
+        <v>0.008019999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.10099</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.13145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.68721</v>
+        <v>0.7715</v>
       </c>
       <c r="D25" t="n">
-        <v>17.43449</v>
+        <v>0.08464000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>17.53597</v>
+        <v>0.62767</v>
       </c>
       <c r="F25" t="n">
-        <v>44.04772</v>
+        <v>0.98551</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0544</v>
+        <v>0.11541</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9242</v>
+        <v>0.00792</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.13175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.50747</v>
+        <v>0.78467</v>
       </c>
       <c r="D26" t="n">
-        <v>16.82465</v>
+        <v>0.08482000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>17.41804</v>
+        <v>0.63812</v>
       </c>
       <c r="F26" t="n">
-        <v>43.92534</v>
+        <v>1.01289</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05342</v>
+        <v>0.11459</v>
       </c>
       <c r="H26" t="n">
-        <v>1.91373</v>
+        <v>0.00791</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09642000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.13176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.5891</v>
+        <v>0.78416</v>
       </c>
       <c r="D27" t="n">
-        <v>17.40921</v>
+        <v>0.08611000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>17.29065</v>
+        <v>0.63753</v>
       </c>
       <c r="F27" t="n">
-        <v>44.98972</v>
+        <v>1.04154</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05329</v>
+        <v>0.11284</v>
       </c>
       <c r="H27" t="n">
-        <v>1.90417</v>
+        <v>0.00813</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.13102</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.5535</v>
+        <v>0.78285</v>
       </c>
       <c r="D28" t="n">
-        <v>17.10752</v>
+        <v>0.08488999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>17.29291</v>
+        <v>0.62986</v>
       </c>
       <c r="F28" t="n">
-        <v>44.60521</v>
+        <v>0.98913</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05262</v>
+        <v>0.11264</v>
       </c>
       <c r="H28" t="n">
-        <v>1.91949</v>
+        <v>0.00801</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.13117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.10567</v>
+        <v>0.76739</v>
       </c>
       <c r="D29" t="n">
-        <v>17.30917</v>
+        <v>0.08497</v>
       </c>
       <c r="E29" t="n">
-        <v>17.79376</v>
+        <v>0.6241</v>
       </c>
       <c r="F29" t="n">
-        <v>43.93876</v>
+        <v>0.99904</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05274</v>
+        <v>0.11561</v>
       </c>
       <c r="H29" t="n">
-        <v>1.86102</v>
+        <v>0.00781</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09754</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.13149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.77757</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08386</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.63275</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.99303</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.11498</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.13094</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>17.68509</v>
-      </c>
-      <c r="D30" t="n">
-        <v>17.81037</v>
-      </c>
-      <c r="E30" t="n">
-        <v>17.49438</v>
-      </c>
-      <c r="F30" t="n">
-        <v>44.25804</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05223</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.87641</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.78264</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.08377</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.63112</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.00486</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.11439</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.007990000000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09669</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.13248</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.08464000000000001</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.64589</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.01131</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.11601</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00796</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09699000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.13222</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.78174</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.08665</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.64416</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.99739</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.11477</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.007939999999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09733</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.13238</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.7936299999999999</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.08369</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.64154</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.01178</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.11468</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09692000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.13156</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.7960199999999999</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.08277</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.6408199999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.00897</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.11472</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09608999999999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.13515</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.76797</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0858</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.63457</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.01483</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.11455</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00797</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09743</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.13111</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.78339</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0854</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.63492</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.00207</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.11488</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.10043</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.13364</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.80292</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08477999999999999</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.64508</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.01343</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.11455</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.008059999999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09898</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.13226</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.7849699999999999</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.08509</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.63557</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.02426</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.11504</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00783</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09782</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.1321</v>
+      <c r="C31" t="n">
+        <v>0.78859</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08416</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.63523</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.00353</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.11247</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09718</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1328</v>
       </c>
     </row>
   </sheetData>
